--- a/results/run_v5.2/results_regression.xlsx
+++ b/results/run_v5.2/results_regression.xlsx
@@ -666,25 +666,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.426785076739397</v>
+        <v>1.426785076739398</v>
       </c>
       <c r="E6" t="n">
-        <v>2.699347136937601</v>
+        <v>2.699347136937599</v>
       </c>
       <c r="F6" t="n">
         <v>1.642969000601533</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7995647579584007</v>
+        <v>-0.7995647579583995</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05837009461398433</v>
+        <v>0.05837009461398438</v>
       </c>
       <c r="I6" t="n">
         <v>1.413016519779388</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.02900517325229623</v>
+        <v>-0.02900517325229823</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.783563765516347</v>
+        <v>3.783563765516349</v>
       </c>
       <c r="E11" t="n">
-        <v>20.36185408462024</v>
+        <v>20.36185408462026</v>
       </c>
       <c r="F11" t="n">
-        <v>4.512411116534069</v>
+        <v>4.512411116534071</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.016570975499295</v>
+        <v>-2.016570975499298</v>
       </c>
       <c r="H11" t="n">
         <v>0.2010925709696538</v>
       </c>
       <c r="I11" t="n">
-        <v>4.255769378451006</v>
+        <v>4.255769378451017</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07855721661765691</v>
+        <v>-0.07855721661765847</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.436865398721348</v>
+        <v>1.436865398721347</v>
       </c>
       <c r="E16" t="n">
-        <v>3.018089652703176</v>
+        <v>3.018089652703171</v>
       </c>
       <c r="F16" t="n">
-        <v>1.737264992078979</v>
+        <v>1.737264992078978</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.389948585750075</v>
+        <v>-3.389948585750067</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05799976600013983</v>
+        <v>0.05799976600013979</v>
       </c>
       <c r="I16" t="n">
         <v>1.247626397229386</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.291810646190645</v>
+        <v>-3.291810646190639</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1281,25 +1281,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.22454310691031</v>
+        <v>2.224543106910313</v>
       </c>
       <c r="E21" t="n">
-        <v>6.290534844897621</v>
+        <v>6.290534844897643</v>
       </c>
       <c r="F21" t="n">
-        <v>2.508093866843428</v>
+        <v>2.508093866843433</v>
       </c>
       <c r="G21" t="n">
-        <v>-32.54951917278731</v>
+        <v>-32.54951917278743</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08596951395478571</v>
+        <v>0.0859695139547858</v>
       </c>
       <c r="I21" t="n">
-        <v>2.671007928600526</v>
+        <v>2.671007928600527</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.767824013882732</v>
+        <v>-9.767824013882704</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1489,22 +1489,22 @@
         <v>4.333319117023031</v>
       </c>
       <c r="E26" t="n">
-        <v>20.4786617514068</v>
+        <v>20.47866175140681</v>
       </c>
       <c r="F26" t="n">
-        <v>4.525335540201058</v>
+        <v>4.525335540201059</v>
       </c>
       <c r="G26" t="n">
-        <v>-80.91464700562722</v>
+        <v>-80.91464700562723</v>
       </c>
       <c r="H26" t="n">
         <v>0.1517471411799529</v>
       </c>
       <c r="I26" t="n">
-        <v>4.190547200815358</v>
+        <v>4.190547200815365</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.804028725798177</v>
+        <v>-5.8040287257982</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1691,25 +1691,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.56858790868231</v>
+        <v>1.568587908682309</v>
       </c>
       <c r="E31" t="n">
-        <v>3.557855505956007</v>
+        <v>3.557855505956003</v>
       </c>
       <c r="F31" t="n">
-        <v>1.886227851018007</v>
+        <v>1.886227851018005</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.108358818344301</v>
+        <v>-1.108358818344299</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06323952304115778</v>
+        <v>0.06323952304115772</v>
       </c>
       <c r="I31" t="n">
-        <v>1.389735260224137</v>
+        <v>1.389735260224132</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.097182184464344</v>
+        <v>-1.097182184464341</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1896,25 +1896,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.114633785052211</v>
+        <v>3.114633785052213</v>
       </c>
       <c r="E36" t="n">
-        <v>15.89676946532169</v>
+        <v>15.8967694653217</v>
       </c>
       <c r="F36" t="n">
-        <v>3.987075302188521</v>
+        <v>3.987075302188522</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.067872450773553</v>
+        <v>-1.067872450773554</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1634522905038216</v>
+        <v>0.1634522905038217</v>
       </c>
       <c r="I36" t="n">
-        <v>3.291611257111407</v>
+        <v>3.291611257111395</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.08413367089990476</v>
+        <v>-0.08413367089990564</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.625432251003832</v>
+        <v>2.625432251003834</v>
       </c>
       <c r="E41" t="n">
-        <v>15.39193698250955</v>
+        <v>15.39193698250958</v>
       </c>
       <c r="F41" t="n">
-        <v>3.923255916010266</v>
+        <v>3.923255916010269</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8108161155893594</v>
+        <v>-0.8108161155893621</v>
       </c>
       <c r="H41" t="n">
-        <v>0.151106109041356</v>
+        <v>0.1511061090413561</v>
       </c>
       <c r="I41" t="n">
-        <v>1.604748813043384</v>
+        <v>1.604748813043388</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0001126496589997084</v>
+        <v>0.000112649658998043</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.823471295731958</v>
+        <v>2.823471295731959</v>
       </c>
       <c r="E46" t="n">
         <v>10.49217827680157</v>
@@ -2315,13 +2315,13 @@
         <v>3.239163206262007</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.238331365717667</v>
+        <v>-1.238331365717668</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1368293443973813</v>
+        <v>0.1368293443973814</v>
       </c>
       <c r="I46" t="n">
-        <v>2.441203173843556</v>
+        <v>2.441203173843563</v>
       </c>
       <c r="J46" t="n">
         <v>0.238947079121678</v>
@@ -2511,25 +2511,25 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.102368192184136</v>
+        <v>5.102368192184125</v>
       </c>
       <c r="E51" t="n">
-        <v>28.47667025794096</v>
+        <v>28.4766702579409</v>
       </c>
       <c r="F51" t="n">
-        <v>5.336353648132866</v>
+        <v>5.336353648132861</v>
       </c>
       <c r="G51" t="n">
-        <v>-21.78133620635277</v>
+        <v>-21.78133620635272</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2658840971771578</v>
+        <v>0.2658840971771573</v>
       </c>
       <c r="I51" t="n">
-        <v>4.937180843724285</v>
+        <v>4.937180843724361</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9540072714628405</v>
+        <v>-0.9540072714628756</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2719,22 +2719,22 @@
         <v>5.048348844406148</v>
       </c>
       <c r="E56" t="n">
-        <v>31.54103476538779</v>
+        <v>31.54103476538778</v>
       </c>
       <c r="F56" t="n">
-        <v>5.616140557837543</v>
+        <v>5.616140557837542</v>
       </c>
       <c r="G56" t="n">
-        <v>-4.734733593706872</v>
+        <v>-4.734733593706869</v>
       </c>
       <c r="H56" t="n">
         <v>0.2870828553083332</v>
       </c>
       <c r="I56" t="n">
-        <v>3.98160743502268</v>
+        <v>3.981607435022674</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1009470382856181</v>
+        <v>-0.1009470382856161</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         <v>4.781750165838188</v>
       </c>
       <c r="E61" t="n">
-        <v>24.67000405609405</v>
+        <v>24.67000405609404</v>
       </c>
       <c r="F61" t="n">
-        <v>4.966890783588265</v>
+        <v>4.966890783588264</v>
       </c>
       <c r="G61" t="n">
         <v>-130.5733549658349</v>
@@ -2939,7 +2939,7 @@
         <v>5.090636268907859</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.625970173869407</v>
+        <v>-8.62597017386938</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2.547339575074678</v>
+        <v>2.547339575074677</v>
       </c>
       <c r="E66" t="n">
         <v>8.430787722526636</v>
@@ -3135,16 +3135,16 @@
         <v>2.903581878047636</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.7985680474723491</v>
+        <v>-0.7985680474723493</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1006879730792589</v>
+        <v>0.1006879730792588</v>
       </c>
       <c r="I66" t="n">
         <v>2.208324086433899</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.5676201401881029</v>
+        <v>-0.5676201401881042</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.275697532303018</v>
+        <v>2.275697532303017</v>
       </c>
       <c r="E71" t="n">
-        <v>6.547723359448488</v>
+        <v>6.547723359448487</v>
       </c>
       <c r="F71" t="n">
         <v>2.558851961221768</v>
       </c>
       <c r="G71" t="n">
-        <v>-5.547723359448488</v>
+        <v>-5.547723359448487</v>
       </c>
       <c r="H71" t="n">
-        <v>0.08692396479926842</v>
+        <v>0.08692396479926837</v>
       </c>
       <c r="I71" t="n">
         <v>2.368805469899394</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.9044897789373709</v>
+        <v>-0.9044897789373718</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3539,19 +3539,19 @@
         <v>5.924872952690611</v>
       </c>
       <c r="E76" t="n">
-        <v>41.11597041426712</v>
+        <v>41.11597041426713</v>
       </c>
       <c r="F76" t="n">
-        <v>6.412173610739741</v>
+        <v>6.412173610739742</v>
       </c>
       <c r="G76" t="n">
-        <v>-5.148182491853028</v>
+        <v>-5.14818249185303</v>
       </c>
       <c r="H76" t="n">
         <v>0.3581556160934248</v>
       </c>
       <c r="I76" t="n">
-        <v>6.312175365835589</v>
+        <v>6.312175365835593</v>
       </c>
       <c r="J76" t="n">
         <v>0.1010316398142252</v>
@@ -3741,25 +3741,25 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2.597669623187106</v>
+        <v>2.597669623187105</v>
       </c>
       <c r="E81" t="n">
-        <v>8.068233158126823</v>
+        <v>8.068233158126819</v>
       </c>
       <c r="F81" t="n">
         <v>2.840463546347114</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.187995432712359</v>
+        <v>-1.187995432712358</v>
       </c>
       <c r="H81" t="n">
-        <v>0.09345133469109669</v>
+        <v>0.09345133469109664</v>
       </c>
       <c r="I81" t="n">
-        <v>2.809275842621421</v>
+        <v>2.809275842621435</v>
       </c>
       <c r="J81" t="n">
-        <v>0.178141513820277</v>
+        <v>0.1781415138202789</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6.930033554316034</v>
+        <v>6.930033554316046</v>
       </c>
       <c r="E86" t="n">
-        <v>56.42905715568742</v>
+        <v>56.42905715568757</v>
       </c>
       <c r="F86" t="n">
-        <v>7.51192765910904</v>
+        <v>7.51192765910905</v>
       </c>
       <c r="G86" t="n">
-        <v>-19.5196571475227</v>
+        <v>-19.51965714752275</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2829818643826104</v>
+        <v>0.2829818643826109</v>
       </c>
       <c r="I86" t="n">
-        <v>7.38189826819899</v>
+        <v>7.381898268198961</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.089868279089974</v>
+        <v>-2.089868279089999</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4151,13 +4151,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3.986193201207708</v>
+        <v>3.986193201207709</v>
       </c>
       <c r="E91" t="n">
-        <v>19.42785616199041</v>
+        <v>19.42785616199043</v>
       </c>
       <c r="F91" t="n">
-        <v>4.407704182677238</v>
+        <v>4.407704182677239</v>
       </c>
       <c r="G91" t="n">
         <v>-10.51280365154988</v>
@@ -4166,10 +4166,10 @@
         <v>0.1363205369084069</v>
       </c>
       <c r="I91" t="n">
-        <v>3.994138391778728</v>
+        <v>3.994138391778733</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.096663659043473</v>
+        <v>-1.096663659043475</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4427,25 +4427,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.956584225210216</v>
+        <v>4.956584225210215</v>
       </c>
       <c r="E6" t="n">
-        <v>37.98853631784572</v>
+        <v>37.98853631784571</v>
       </c>
       <c r="F6" t="n">
-        <v>6.163484105426551</v>
+        <v>6.16348410542655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.038264903345678</v>
+        <v>0.03826490334567823</v>
       </c>
       <c r="H6" t="n">
         <v>0.2113895211848695</v>
       </c>
       <c r="I6" t="n">
-        <v>4.851561176877214</v>
+        <v>4.851561176877215</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03890705815564766</v>
+        <v>0.03890705815564788</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4647,10 +4647,10 @@
         <v>0.3460839352972096</v>
       </c>
       <c r="I11" t="n">
-        <v>15.7205431861471</v>
+        <v>15.72054318614711</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1360140752994636</v>
+        <v>-0.1360140752994623</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.55677558198968</v>
+        <v>19.55677558198969</v>
       </c>
       <c r="E16" t="n">
-        <v>382.7468081505028</v>
+        <v>382.7468081505029</v>
       </c>
       <c r="F16" t="n">
         <v>19.56391597177065</v>
@@ -4849,10 +4849,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.407432824624785</v>
+        <v>0.4074328246247851</v>
       </c>
       <c r="I16" t="n">
-        <v>19.69988405205156</v>
+        <v>19.69988405205157</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
         <v>7.86529141958608</v>
       </c>
       <c r="E21" t="n">
-        <v>71.32600211552993</v>
+        <v>71.32600211552995</v>
       </c>
       <c r="F21" t="n">
         <v>8.445472284930544</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.838069257314473</v>
+        <v>-8.838069257314475</v>
       </c>
       <c r="H21" t="n">
         <v>0.3925842568566155</v>
       </c>
       <c r="I21" t="n">
-        <v>6.592211594036064</v>
+        <v>6.592211594036019</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3052680000711061</v>
+        <v>-0.3052680000711074</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.30345500418777</v>
+        <v>16.30345500418778</v>
       </c>
       <c r="E26" t="n">
         <v>269.2551398272329</v>
@@ -5259,13 +5259,13 @@
         <v>-72.01834300399535</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3633896095399751</v>
+        <v>0.3633896095399752</v>
       </c>
       <c r="I26" t="n">
         <v>15.41370300562386</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06373023629626318</v>
+        <v>0.06373023629626262</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.542605132792083</v>
+        <v>3.542605132792086</v>
       </c>
       <c r="E31" t="n">
         <v>26.36896861761056</v>
@@ -5461,16 +5461,16 @@
         <v>5.135072406267565</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1719541607826913</v>
+        <v>-0.1719541607826918</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1021998064741073</v>
+        <v>0.1021998064741074</v>
       </c>
       <c r="I31" t="n">
-        <v>1.745167369827978</v>
+        <v>1.745167369828005</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.05181518540148655</v>
+        <v>-0.05181518540148722</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5657,25 +5657,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.363930708019056</v>
+        <v>3.363930708019057</v>
       </c>
       <c r="E36" t="n">
-        <v>12.40495548539489</v>
+        <v>12.4049554853949</v>
       </c>
       <c r="F36" t="n">
-        <v>3.522066933690342</v>
+        <v>3.522066933690343</v>
       </c>
       <c r="G36" t="n">
-        <v>-15.53994064719318</v>
+        <v>-15.53994064719319</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1062891592350633</v>
+        <v>0.1062891592350634</v>
       </c>
       <c r="I36" t="n">
         <v>3.465082789089971</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4519009027217402</v>
+        <v>-0.4519009027217351</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5862,25 +5862,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.560504542404542</v>
+        <v>2.560504542404541</v>
       </c>
       <c r="E41" t="n">
-        <v>10.86713194416233</v>
+        <v>10.86713194416231</v>
       </c>
       <c r="F41" t="n">
-        <v>3.296533322167749</v>
+        <v>3.296533322167745</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.094868808513221</v>
+        <v>-1.094868808513216</v>
       </c>
       <c r="H41" t="n">
         <v>0.1050959806615226</v>
       </c>
       <c r="I41" t="n">
-        <v>2.477413628410391</v>
+        <v>2.477413628410375</v>
       </c>
       <c r="J41" t="n">
-        <v>0.00832017590809897</v>
+        <v>0.008320175908099636</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -6070,22 +6070,22 @@
         <v>8.454137472077424</v>
       </c>
       <c r="E46" t="n">
-        <v>74.00090376071891</v>
+        <v>74.00090376071896</v>
       </c>
       <c r="F46" t="n">
-        <v>8.602377796907023</v>
+        <v>8.602377796907025</v>
       </c>
       <c r="G46" t="n">
-        <v>-48.33393584047928</v>
+        <v>-48.3339358404793</v>
       </c>
       <c r="H46" t="n">
         <v>0.4074802442193892</v>
       </c>
       <c r="I46" t="n">
-        <v>9.065691480566327</v>
+        <v>9.065691480566313</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.6856422426235209</v>
+        <v>-0.6856422426235265</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6275,22 +6275,22 @@
         <v>3.553523052308603</v>
       </c>
       <c r="E51" t="n">
-        <v>14.27168955152437</v>
+        <v>14.27168955152436</v>
       </c>
       <c r="F51" t="n">
         <v>3.777788976574044</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1417351641219493</v>
+        <v>-0.1417351641219489</v>
       </c>
       <c r="H51" t="n">
         <v>0.1269074592695634</v>
       </c>
       <c r="I51" t="n">
-        <v>3.757918295101881</v>
+        <v>3.757918295101891</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.02376236392220399</v>
+        <v>-0.02376236392220354</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6480,22 +6480,22 @@
         <v>16.87761384668778</v>
       </c>
       <c r="E56" t="n">
-        <v>301.9174359340615</v>
+        <v>301.9174359340618</v>
       </c>
       <c r="F56" t="n">
-        <v>17.37577152054151</v>
+        <v>17.37577152054152</v>
       </c>
       <c r="G56" t="n">
-        <v>-17.09243061777147</v>
+        <v>-17.09243061777149</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3716847553877383</v>
+        <v>0.3716847553877385</v>
       </c>
       <c r="I56" t="n">
-        <v>18.28800490966173</v>
+        <v>18.28800490966172</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.02253703527517681</v>
+        <v>-0.02253703527517459</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6682,25 +6682,25 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8.140550881561344</v>
+        <v>8.140550881561348</v>
       </c>
       <c r="E61" t="n">
-        <v>87.62503203143135</v>
+        <v>87.62503203143137</v>
       </c>
       <c r="F61" t="n">
-        <v>9.360824324354738</v>
+        <v>9.36082432435474</v>
       </c>
       <c r="G61" t="n">
-        <v>-2.054467347500875</v>
+        <v>-2.054467347500876</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4536807145867715</v>
+        <v>0.4536807145867716</v>
       </c>
       <c r="I61" t="n">
-        <v>9.08773646609608</v>
+        <v>9.087736466096095</v>
       </c>
       <c r="J61" t="n">
-        <v>0.004063852176770744</v>
+        <v>0.004063852176770522</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6887,16 +6887,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.268967760401935</v>
+        <v>5.268967760401934</v>
       </c>
       <c r="E66" t="n">
-        <v>37.22764451783281</v>
+        <v>37.22764451783279</v>
       </c>
       <c r="F66" t="n">
-        <v>6.101446100543117</v>
+        <v>6.101446100543116</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.441157017562808</v>
+        <v>-1.441157017562806</v>
       </c>
       <c r="H66" t="n">
         <v>0.1491069043274358</v>
@@ -6905,7 +6905,7 @@
         <v>5.105023436794005</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.136239974681672</v>
+        <v>-0.1362399746816714</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8.710491852773631</v>
+        <v>8.710491852773629</v>
       </c>
       <c r="E71" t="n">
         <v>78.5040791106899</v>
@@ -7110,7 +7110,7 @@
         <v>9.350087461221351</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.2029306484361675</v>
+        <v>-0.2029306484361699</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -7303,19 +7303,19 @@
         <v>144.9979640477378</v>
       </c>
       <c r="F76" t="n">
-        <v>12.04151004017925</v>
+        <v>12.04151004017926</v>
       </c>
       <c r="G76" t="n">
-        <v>-65.28478356468013</v>
+        <v>-65.28478356468014</v>
       </c>
       <c r="H76" t="n">
         <v>0.7052959554197434</v>
       </c>
       <c r="I76" t="n">
-        <v>11.78105782528214</v>
+        <v>11.78105782528216</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.02566773673036393</v>
+        <v>-0.02566773673036593</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -7502,25 +7502,25 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.710580036659005</v>
+        <v>4.710580036659006</v>
       </c>
       <c r="E81" t="n">
-        <v>32.81081948419356</v>
+        <v>32.81081948419355</v>
       </c>
       <c r="F81" t="n">
-        <v>5.72807292937106</v>
+        <v>5.728072929371059</v>
       </c>
       <c r="G81" t="n">
-        <v>-2.201055559433518</v>
+        <v>-2.201055559433517</v>
       </c>
       <c r="H81" t="n">
         <v>0.2041375404500308</v>
       </c>
       <c r="I81" t="n">
-        <v>3.027426032805446</v>
+        <v>3.02742603280546</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.2418665266270097</v>
+        <v>-0.2418665266270092</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7707,25 +7707,25 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4.663209577588863</v>
+        <v>4.663209577588865</v>
       </c>
       <c r="E86" t="n">
-        <v>31.92139485493988</v>
+        <v>31.92139485493991</v>
       </c>
       <c r="F86" t="n">
-        <v>5.649902198705734</v>
+        <v>5.649902198705736</v>
       </c>
       <c r="G86" t="n">
-        <v>0.02530092045985088</v>
+        <v>0.02530092045985011</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2029893391945281</v>
+        <v>0.2029893391945282</v>
       </c>
       <c r="I86" t="n">
-        <v>4.846402940847209</v>
+        <v>4.84640294084719</v>
       </c>
       <c r="J86" t="n">
-        <v>0.02581868910092777</v>
+        <v>0.02581868910092711</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7912,25 +7912,25 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.138266346316574</v>
+        <v>2.138266346316575</v>
       </c>
       <c r="E91" t="n">
-        <v>6.080180632145572</v>
+        <v>6.080180632145578</v>
       </c>
       <c r="F91" t="n">
-        <v>2.465802228919743</v>
+        <v>2.465802228919744</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.4519834345422262</v>
+        <v>-0.4519834345422276</v>
       </c>
       <c r="H91" t="n">
-        <v>0.06951392183658982</v>
+        <v>0.06951392183658983</v>
       </c>
       <c r="I91" t="n">
-        <v>2.435402237359549</v>
+        <v>2.435402237359558</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.03709054235033671</v>
+        <v>-0.03709054235033649</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -8191,22 +8191,22 @@
         <v>1.659725951597444</v>
       </c>
       <c r="E6" t="n">
-        <v>3.650451166113027</v>
+        <v>3.650451166113039</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91061538937407</v>
+        <v>1.910615389374073</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.433634110742018</v>
+        <v>-1.433634110742026</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06538264828070997</v>
+        <v>0.06538264828071001</v>
       </c>
       <c r="I6" t="n">
         <v>1.776395802497609</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1218610188123022</v>
+        <v>-0.1218610188123046</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8396,13 +8396,13 @@
         <v>8.316273297110994</v>
       </c>
       <c r="E11" t="n">
-        <v>73.01960305766066</v>
+        <v>73.01960305766065</v>
       </c>
       <c r="F11" t="n">
         <v>8.545150850491796</v>
       </c>
       <c r="G11" t="n">
-        <v>-18.80192625292493</v>
+        <v>-18.80192625292492</v>
       </c>
       <c r="H11" t="n">
         <v>0.4457827926164852</v>
@@ -8411,7 +8411,7 @@
         <v>7.891024356641406</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.04656312011370245</v>
+        <v>-0.04656312011370645</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8598,22 +8598,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.470789463557602</v>
+        <v>0.4707894635576038</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3085038308377343</v>
+        <v>0.308503830837735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.555431211616465</v>
+        <v>0.5554312116164656</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0168139094127715</v>
+        <v>0.01681390941277156</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3989785005311486</v>
+        <v>0.3989785005311504</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -8806,7 +8806,7 @@
         <v>13.74165964527026</v>
       </c>
       <c r="E21" t="n">
-        <v>190.1938768970863</v>
+        <v>190.1938768970864</v>
       </c>
       <c r="F21" t="n">
         <v>13.79107961318063</v>
@@ -8821,7 +8821,7 @@
         <v>13.90664011579517</v>
       </c>
       <c r="J21" t="n">
-        <v>0.09288860624181228</v>
+        <v>0.09288860624180939</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.85054070115692</v>
+        <v>12.85054070115691</v>
       </c>
       <c r="E26" t="n">
         <v>185.4276516178061</v>
@@ -9017,16 +9017,16 @@
         <v>13.61718222018807</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.663981843273284</v>
+        <v>-8.66398184327328</v>
       </c>
       <c r="H26" t="n">
         <v>0.3110114719665789</v>
       </c>
       <c r="I26" t="n">
-        <v>12.12370749564148</v>
+        <v>12.12370749564147</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.05752470648680985</v>
+        <v>-0.05752470648681052</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -9213,25 +9213,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.303055488012632</v>
+        <v>6.303055488012627</v>
       </c>
       <c r="E31" t="n">
-        <v>64.61277121911903</v>
+        <v>64.61277121911893</v>
       </c>
       <c r="F31" t="n">
-        <v>8.03820696543197</v>
+        <v>8.038206965431963</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.637255968127307</v>
+        <v>-1.637255968127303</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1692570522381162</v>
+        <v>0.169257052238116</v>
       </c>
       <c r="I31" t="n">
         <v>4.877223491754556</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.015684193230729</v>
+        <v>-0.01568419323072767</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>0.1689986608462453</v>
       </c>
       <c r="I36" t="n">
-        <v>6.096437902412518</v>
+        <v>6.096437902412511</v>
       </c>
       <c r="J36" t="n">
         <v>0.0510071988597891</v>
@@ -9626,7 +9626,7 @@
         <v>4.8017621066738</v>
       </c>
       <c r="E41" t="n">
-        <v>30.60372698151639</v>
+        <v>30.60372698151638</v>
       </c>
       <c r="F41" t="n">
         <v>5.532063537371601</v>
@@ -9638,10 +9638,10 @@
         <v>0.2255705261087477</v>
       </c>
       <c r="I41" t="n">
-        <v>5.443923339816489</v>
+        <v>5.443923339816475</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.006241020323730639</v>
+        <v>-0.006241020323730417</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -9828,25 +9828,25 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9.253611476976062</v>
+        <v>9.25361147697606</v>
       </c>
       <c r="E46" t="n">
-        <v>88.75109603985295</v>
+        <v>88.75109603985292</v>
       </c>
       <c r="F46" t="n">
         <v>9.420780012284171</v>
       </c>
       <c r="G46" t="n">
-        <v>-31.2731258326738</v>
+        <v>-31.27312583267379</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5120177169434625</v>
+        <v>0.5120177169434624</v>
       </c>
       <c r="I46" t="n">
-        <v>9.316939076729131</v>
+        <v>9.316939076729117</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.1351893356472262</v>
+        <v>-0.1351893356472282</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -10036,22 +10036,22 @@
         <v>8.376379254573434</v>
       </c>
       <c r="E51" t="n">
-        <v>95.89901254253979</v>
+        <v>95.89901254253974</v>
       </c>
       <c r="F51" t="n">
-        <v>9.792804120502963</v>
+        <v>9.792804120502959</v>
       </c>
       <c r="G51" t="n">
-        <v>-2.27859871940307</v>
+        <v>-2.278598719403068</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5338706718237262</v>
+        <v>0.5338706718237261</v>
       </c>
       <c r="I51" t="n">
-        <v>9.196138672960192</v>
+        <v>9.196138672960206</v>
       </c>
       <c r="J51" t="n">
-        <v>0.01630338009285315</v>
+        <v>0.0163033800928537</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -10250,13 +10250,13 @@
         <v>-58.18623787106955</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3957078406272641</v>
+        <v>0.3957078406272642</v>
       </c>
       <c r="I56" t="n">
         <v>18.44579701924901</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.05083213644039852</v>
+        <v>-0.05083213644039741</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -10446,19 +10446,19 @@
         <v>6.199536464738157</v>
       </c>
       <c r="E61" t="n">
-        <v>47.87967031009022</v>
+        <v>47.87967031009024</v>
       </c>
       <c r="F61" t="n">
-        <v>6.919513733644165</v>
+        <v>6.919513733644167</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0959581186858991</v>
+        <v>-0.09595811868589954</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3011140235901398</v>
+        <v>0.3011140235901399</v>
       </c>
       <c r="I61" t="n">
-        <v>5.092855062818444</v>
+        <v>5.092855062818446</v>
       </c>
       <c r="J61" t="n">
         <v>1.368712897564794e-05</v>
@@ -10648,25 +10648,25 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.82629467002502</v>
+        <v>1.826294670025021</v>
       </c>
       <c r="E66" t="n">
-        <v>4.887605610912483</v>
+        <v>4.887605610912486</v>
       </c>
       <c r="F66" t="n">
         <v>2.210792982373629</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.08613458020277398</v>
+        <v>-0.08613458020277465</v>
       </c>
       <c r="H66" t="n">
-        <v>0.06602200810375129</v>
+        <v>0.06602200810375128</v>
       </c>
       <c r="I66" t="n">
-        <v>1.90793297076039</v>
+        <v>1.907932970760383</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.07600490956428896</v>
+        <v>-0.07600490956428985</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -10853,16 +10853,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.56576603804724</v>
+        <v>2.565766038047243</v>
       </c>
       <c r="E71" t="n">
         <v>14.72670150931469</v>
       </c>
       <c r="F71" t="n">
-        <v>3.837538470076188</v>
+        <v>3.837538470076189</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.07592339794079916</v>
+        <v>-0.07592339794079961</v>
       </c>
       <c r="H71" t="n">
         <v>0.1172145281264111</v>
@@ -10871,7 +10871,7 @@
         <v>1.158576086588782</v>
       </c>
       <c r="J71" t="n">
-        <v>0.03103506279543122</v>
+        <v>0.03103506279543056</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -11061,22 +11061,22 @@
         <v>2.027258906290037</v>
       </c>
       <c r="E76" t="n">
-        <v>5.305650817926831</v>
+        <v>5.305650817926825</v>
       </c>
       <c r="F76" t="n">
-        <v>2.303399838917862</v>
+        <v>2.30339983891786</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.425440373909408</v>
+        <v>-1.425440373909406</v>
       </c>
       <c r="H76" t="n">
-        <v>0.08118271828498934</v>
+        <v>0.08118271828498932</v>
       </c>
       <c r="I76" t="n">
-        <v>2.144026613731244</v>
+        <v>2.144026613731242</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.07702489733931506</v>
+        <v>-0.07702489733931484</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -11269,19 +11269,19 @@
         <v>14.44728506287183</v>
       </c>
       <c r="F81" t="n">
-        <v>3.800958440034806</v>
+        <v>3.800958440034807</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.540181989076365</v>
+        <v>-1.540181989076366</v>
       </c>
       <c r="H81" t="n">
         <v>0.1309905519847274</v>
       </c>
       <c r="I81" t="n">
-        <v>3.13474226979667</v>
+        <v>3.134742269796648</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.1431248746066056</v>
+        <v>-0.1431248746066058</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -11468,25 +11468,25 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2.534658339455433</v>
+        <v>2.534658339455432</v>
       </c>
       <c r="E86" t="n">
-        <v>8.925522347738704</v>
+        <v>8.92552234773871</v>
       </c>
       <c r="F86" t="n">
-        <v>2.987561270959761</v>
+        <v>2.987561270959762</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.245644490086802</v>
+        <v>-2.245644490086804</v>
       </c>
       <c r="H86" t="n">
-        <v>0.09491543582974339</v>
+        <v>0.09491543582974336</v>
       </c>
       <c r="I86" t="n">
-        <v>2.440899850360534</v>
+        <v>2.440899850360548</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.41149866231239</v>
+        <v>-1.411498662312393</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -11688,10 +11688,10 @@
         <v>0.2183723642103957</v>
       </c>
       <c r="I91" t="n">
-        <v>5.151502858151662</v>
+        <v>5.151502858151645</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.8939785119350339</v>
+        <v>-0.8939785119350376</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
